--- a/p6_deployment/data/italy/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/p6_deployment/data/italy/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A25"/>
+  <dimension ref="A2:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -487,112 +487,196 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
+          <t>t4ZkclrT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
+          <t>EirZ0Wr4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>f9bfyqFM</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>bHLf4sq9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>WlhYT07d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>SzxylMbS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>hvcjgHz8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>bs5ow5pA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>Ob5Zdayq</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>dC3sew6e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>6sP22LDL</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>bepKi4a3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>ILr8tvi2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
           <t>fNwTkrUF</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/italy/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/p6_deployment/data/italy/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -515,14 +515,14 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>SzxylMbS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>WlhYT07d</t>
         </is>
       </c>
     </row>
